--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -9,12 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Machines" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$F$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Machines'!$A$1:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,7 +480,6 @@
           <t>INR</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Currency shown on cost results</t>
@@ -2449,413 +2446,4 @@
   <autoFilter ref="A1:F23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="59" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>part_type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>machine</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tonnage_t</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>length_mm</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>width_mm</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>mhr_per_hour</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>plastic</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IMM 80 T</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D2" t="n">
-        <v>320</v>
-      </c>
-      <c r="E2" t="n">
-        <v>320</v>
-      </c>
-      <c r="F2" t="n">
-        <v>550</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>plastic</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IMM 150 T</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D3" t="n">
-        <v>420</v>
-      </c>
-      <c r="E3" t="n">
-        <v>420</v>
-      </c>
-      <c r="F3" t="n">
-        <v>750</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>plastic</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IMM 250 T</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>250</v>
-      </c>
-      <c r="D4" t="n">
-        <v>560</v>
-      </c>
-      <c r="E4" t="n">
-        <v>560</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>plastic</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IMM 450 T</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>450</v>
-      </c>
-      <c r="D5" t="n">
-        <v>760</v>
-      </c>
-      <c r="E5" t="n">
-        <v>760</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>die_casting</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>HPDC 250 T</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>250</v>
-      </c>
-      <c r="D6" t="n">
-        <v>560</v>
-      </c>
-      <c r="E6" t="n">
-        <v>560</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>die_casting</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HPDC 400 T</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>400</v>
-      </c>
-      <c r="D7" t="n">
-        <v>710</v>
-      </c>
-      <c r="E7" t="n">
-        <v>710</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>die_casting</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>HPDC 800 T</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>800</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3800</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>foundry</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Automatic moulding line 600 x 500 flask</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>600</v>
-      </c>
-      <c r="E9" t="n">
-        <v>500</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>foundry</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Hand moulding bay 1000 x 800 flask</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E10" t="n">
-        <v>800</v>
-      </c>
-      <c r="F10" t="n">
-        <v>900</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sheet_metal</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Power press 100 T</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>100</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E11" t="n">
-        <v>600</v>
-      </c>
-      <c r="F11" t="n">
-        <v>600</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sheet_metal</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Power press 200 T</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>200</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E12" t="n">
-        <v>800</v>
-      </c>
-      <c r="F12" t="n">
-        <v>900</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>sheet_metal</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Power press 400 T</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>400</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Example machine - replace with your plant / supplier list</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G13"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$F$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00102A43"/>
+        <fgColor rgb="000E1A2C"/>
       </patternFill>
     </fill>
   </fills>
@@ -480,6 +480,7 @@
           <t>INR</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Currency shown on cost results</t>
@@ -1827,15 +1828,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1856,16 +1855,6 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>rate_per_kg</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>scrap_rate_per_kg</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>notes</t>
         </is>
       </c>
@@ -1884,15 +1873,9 @@
       <c r="C2" t="n">
         <v>0.905</v>
       </c>
-      <c r="D2" t="n">
-        <v>110</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -1910,15 +1893,9 @@
       <c r="C3" t="n">
         <v>1.04</v>
       </c>
-      <c r="D3" t="n">
-        <v>180</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -1936,15 +1913,9 @@
       <c r="C4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D4" t="n">
-        <v>260</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -1962,15 +1933,9 @@
       <c r="C5" t="n">
         <v>1.13</v>
       </c>
-      <c r="D5" t="n">
-        <v>230</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -1988,15 +1953,9 @@
       <c r="C6" t="n">
         <v>1.13</v>
       </c>
-      <c r="D6" t="n">
-        <v>250</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2014,15 +1973,9 @@
       <c r="C7" t="n">
         <v>1.36</v>
       </c>
-      <c r="D7" t="n">
-        <v>330</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2040,15 +1993,9 @@
       <c r="C8" t="n">
         <v>1.53</v>
       </c>
-      <c r="D8" t="n">
-        <v>300</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2066,15 +2013,9 @@
       <c r="C9" t="n">
         <v>1.41</v>
       </c>
-      <c r="D9" t="n">
-        <v>220</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2092,15 +2033,9 @@
       <c r="C10" t="n">
         <v>2.74</v>
       </c>
-      <c r="D10" t="n">
-        <v>260</v>
-      </c>
-      <c r="E10" t="n">
-        <v>180</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2053,9 @@
       <c r="C11" t="n">
         <v>2.71</v>
       </c>
-      <c r="D11" t="n">
-        <v>265</v>
-      </c>
-      <c r="E11" t="n">
-        <v>180</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2144,15 +2073,9 @@
       <c r="C12" t="n">
         <v>6.6</v>
       </c>
-      <c r="D12" t="n">
-        <v>300</v>
-      </c>
-      <c r="E12" t="n">
-        <v>220</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2170,15 +2093,9 @@
       <c r="C13" t="n">
         <v>1.81</v>
       </c>
-      <c r="D13" t="n">
-        <v>500</v>
-      </c>
-      <c r="E13" t="n">
-        <v>300</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2196,15 +2113,9 @@
       <c r="C14" t="n">
         <v>7.2</v>
       </c>
-      <c r="D14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E14" t="n">
-        <v>40</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2222,15 +2133,9 @@
       <c r="C15" t="n">
         <v>7.1</v>
       </c>
-      <c r="D15" t="n">
-        <v>55</v>
-      </c>
-      <c r="E15" t="n">
-        <v>45</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2248,15 +2153,9 @@
       <c r="C16" t="n">
         <v>7.85</v>
       </c>
-      <c r="D16" t="n">
-        <v>65</v>
-      </c>
-      <c r="E16" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2274,15 +2173,9 @@
       <c r="C17" t="n">
         <v>2.68</v>
       </c>
-      <c r="D17" t="n">
-        <v>250</v>
-      </c>
-      <c r="E17" t="n">
-        <v>170</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2300,15 +2193,9 @@
       <c r="C18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="D18" t="n">
-        <v>750</v>
-      </c>
-      <c r="E18" t="n">
-        <v>550</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2213,9 @@
       <c r="C19" t="n">
         <v>7.85</v>
       </c>
-      <c r="D19" t="n">
-        <v>65</v>
-      </c>
-      <c r="E19" t="n">
-        <v>30</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2352,15 +2233,9 @@
       <c r="C20" t="n">
         <v>7.85</v>
       </c>
-      <c r="D20" t="n">
-        <v>72</v>
-      </c>
-      <c r="E20" t="n">
-        <v>30</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2378,15 +2253,9 @@
       <c r="C21" t="n">
         <v>7.93</v>
       </c>
-      <c r="D21" t="n">
-        <v>230</v>
-      </c>
-      <c r="E21" t="n">
-        <v>110</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2404,15 +2273,9 @@
       <c r="C22" t="n">
         <v>2.68</v>
       </c>
-      <c r="D22" t="n">
-        <v>300</v>
-      </c>
-      <c r="E22" t="n">
-        <v>150</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
@@ -2430,20 +2293,14 @@
       <c r="C23" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="D23" t="n">
-        <v>850</v>
-      </c>
-      <c r="E23" t="n">
-        <v>650</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Example rate - replace with your current price</t>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F23"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Materials" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1816,8 +1816,204 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>trial_machine_process</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Injection moulding</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Stage 4 try-out: process name of the machines (Machines sheet) the try-out machine is chosen from</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Stage 4 number of tool trials (T0, T1, T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>trial_hours_each</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Stage 4 machine hours per trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>trial_shots_each</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>200</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>shots</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Stage 4 shots per trial (material)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>trial_machine_process</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Die casting</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Stage 4 try-out: process name of the machines (Machines sheet) the try-out machine is chosen from</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Stage 4 number of tool trials (T0, T1, T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>trial_hours_each</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Stage 4 machine hours per trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>trial_shots_each</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>100</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>shots</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Stage 4 shots per trial (material)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E55"/>
+  <autoFilter ref="A1:E63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2012,8 +2012,181 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>operator_grade</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>operator</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Labour grade of the moulding / casting operator (Labour grades)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>operators_per_machine</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>persons</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Operators per machine (0.5 = one operator runs two machines)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>secondary_ops_pct</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>% of process</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Secondary operations (deburr, inspection, assembly) as % of the process cost; typed per part to override</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>rejection_pct</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Process rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>rejection_pct</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Process rejection (porosity, trimming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>part_overhead_pct</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>% of conversion</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Admin / selling overhead on process + secondary cost (factory overhead is already in the MHR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>packing_pct</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Packing as % of the ex-works cost before packing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E63"/>
+  <autoFilter ref="A1:E70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,11 +427,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
@@ -2185,8 +2185,231 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>press_machine_process</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Press</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Machines process that takes sheet-metal press tonnage</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>stripping_pct</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>10</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>% of cutting</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stripping force as % of the cutting force</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>progressive_min_volume</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>parts/yr</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Progressive die when the annual volume is at least this</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>progressive_max_len_mm</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>300</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Progressive die only up to this part length</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>progressive_max_draw_mm</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>15</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Progressive die only up to this draw depth (deeper: multi-stage / transfer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>default_bend_radius_factor</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>× t</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Inside bend radius assumed when the model has sharp corners</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>draw_height_ratio</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>× t</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>EXAMPLE: A part without bends taller than this × thickness is treated as drawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>bend_angle_deg</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>90</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Bend angle assumed for the springback estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>max_springback_deg</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Flag springback above this</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E70"/>
+  <autoFilter ref="A1:E79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2408,8 +2408,233 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>bridge_min_mm</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Smallest bridge between blanks in the strip</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>bridge_t_factor</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>× t</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Bridge as a multiple of thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>edge_min_mm</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Smallest edge margin on each side of the strip</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>edge_t_factor</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>× t</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Edge margin as a multiple of thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>carrier_mm</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Extra carrier width across the strip</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>idle_stations</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>stations</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Idle stations in the die (strength, clearance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>pilots</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Pilot holes per pitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>pilot_min_dia_mm</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Smallest pilot diameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>strip_max_width_mm</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>300</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Widest strip the line takes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E79"/>
+  <autoFilter ref="A1:E88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2633,8 +2633,58 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>igst_claimable</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1 = yes</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>EXAMPLE: 1 if the IGST paid on import is claimable as input credit (shown separately)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>fx_scenario_pct</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Forex scenario ± shown in the country comparison</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E88"/>
+  <autoFilter ref="A1:E90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2683,8 +2683,33 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>pcb_panel_waste_pct</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>15</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Bare-board panel waste and set-up share added to the board cost</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E90"/>
+  <autoFilter ref="A1:E91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2708,8 +2708,1067 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>runner_pct</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Trim, flash and fines</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>process_loss_pct</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Start-up and reject loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>cycle_time_s</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>150</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>EXAMPLE: EPS moulding cycle: fill, steam, cooling, demould</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>oee_pct</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>70</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>EXAMPLE: OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>max_cavities</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>cavities</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Blocks per chest</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>plate_length_mm</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Steam chest inner length</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>plate_width_mm</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Steam chest inner width</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>spacing_mm</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>40</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Spacing between blocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>tool_life_shots</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>shots</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Aluminium tool life</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>standard_cavities</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 6, 8</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Allowed cavity counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>cycle_base_s</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>8</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stage C rule: cycle = base + cooling factor x wall^2 (fill, open, eject time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>cooling_factor_s_per_mm2</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>s/mm2</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stage C rule: cooling time per mm^2 of main wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>cavity_pressure_bar</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Steam pressure on the projected area</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>clamp_safety_factor</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Locking safety factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>trial_machine_process</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EPS moulding</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Machine process used for try-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Try-outs</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>trial_hours_each</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>6</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Hours per try-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>trial_shots_each</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>30</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>shots</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Shots per try-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>steam_kg_per_kg_part</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>kg/kg</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Steam per kg of moulded EPS (pre-expansion and moulding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>rejection_pct</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Process rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>runner_pct</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Preform gate and neck allowance</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>process_loss_pct</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Start-up and reject loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>cycle_time_s</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>6</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Cycle per shot of all cavities</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>oee_pct</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>80</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>EXAMPLE: OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>max_cavities</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>cavities</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Cavities of the largest machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>plate_length_mm</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Mould area length</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>plate_width_mm</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>800</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Mould area width</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>spacing_mm</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>40</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Spacing between cavities</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>tool_life_shots</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>shots</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Blow mould life</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>standard_cavities</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 6, 8, 10, 12, 16</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Allowed cavity counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>cycle_base_s</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>8</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stage C rule: cycle = base + cooling factor x wall^2 (fill, open, eject time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>cooling_factor_s_per_mm2</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>s/mm2</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stage C rule: cooling time per mm^2 of main wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>cavity_pressure_bar</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>35</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Blow pressure on the projected area</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>clamp_safety_factor</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Locking safety factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>trial_machine_process</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Stretch blow moulding</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Machine process used for try-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Try-outs</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>trial_hours_each</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>4</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Hours per try-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>trial_shots_each</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>500</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>shots</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Shots per try-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>blow_wall_mm</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Average bottle wall (weight = outer surface x wall x density)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>preform_conversion_pct</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>28</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>% of resin</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Preform injection moulding conversion (machine, labour, tool, margin) as % of resin cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>rejection_pct</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Process rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>steam_kg_per_kg_part</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>kg/kg</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Steam per kg of moulded part (EPS only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>preform_conversion_pct</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>% of resin</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Preform conversion (bottles only)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E91"/>
+  <autoFilter ref="A1:E134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2720,11 +3779,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
@@ -3191,8 +4250,108 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EPS bead grade S (20 kg/m3)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EXAMPLE density. Foamed part density. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EPS bead grade F, flame retardant (25 kg/m3)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EXAMPLE density. Foamed part density. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PET bottle grade (IV 0.80)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EXAMPLE density. Resin density, used for the shell weight. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>blow</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rPET food grade</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EXAMPLE density. Resin density. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PET preform grade</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EXAMPLE density. For preform injection moulding. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3767,8 +3767,33 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>later_draw_ratio</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Reduction ratio of every draw after the first (EXAMPLE)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E134"/>
+  <autoFilter ref="A1:E135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3792,8 +3792,371 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>fea_e_mpa</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Young's modulus of tool steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>fea_poisson</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Poisson's ratio of tool steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>fea_yield_mpa</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>800</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Yield strength of the insert steel (EXAMPLE: pre-hardened P20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>fea_safety</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Safety factor on yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>fea_max_deflection_mm</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Allowed elastic deflection of an insert or die block</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>fea_e_mpa</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Young's modulus of tool steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>fea_poisson</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Poisson's ratio of tool steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>fea_yield_mpa</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>800</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Yield strength of the insert steel (EXAMPLE: pre-hardened P20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>fea_safety</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Safety factor on yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>fea_max_deflection_mm</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Allowed elastic deflection of an insert or die block</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>fea_e_mpa</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Young's modulus of tool steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>fea_poisson</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Poisson's ratio of tool steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>fea_yield_mpa</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>800</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Yield strength of the insert steel (EXAMPLE: pre-hardened P20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>fea_safety</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Safety factor on yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>fea_max_deflection_mm</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Allowed elastic deflection of an insert or die block</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E135"/>
+  <autoFilter ref="A1:E150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4155,8 +4155,133 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>spm_progressive</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>60</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>strokes/min</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Strokes per minute of the progressive die</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>spm_stage</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>25</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>parts/min</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Parts per minute of one stage die (feeding by hand or robot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>operators_stage_press</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>persons</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Operators per press in a stage line (progressive uses operators_per_machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>scrap_credit_pct</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>40</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Scrap sold at this % of the material rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>tool_markup_pct</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>25</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Toolroom design, try-out, overhead and margin on the tool made-parts cost</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E150"/>
+  <autoFilter ref="A1:E155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$134</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3779,13 +3779,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3801,10 +3803,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>material_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>density_g_cm3</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -3821,10 +3833,20 @@
           <t>PP (polypropylene)</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Polypropylene (PP)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0.905</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -3841,10 +3863,20 @@
           <t>ABS</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1.04</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -3861,10 +3893,20 @@
           <t>PC (polycarbonate)</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Polycarbonate (PC)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -3881,10 +3923,20 @@
           <t>PC/ABS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PC/ABS blend</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>1.13</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -3901,10 +3953,20 @@
           <t>PA6</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Polyamide (PA)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>1.13</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -3921,10 +3983,20 @@
           <t>PA66 GF30</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Polyamide glass-filled (PA GF)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>1.36</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -3941,10 +4013,20 @@
           <t>PBT GF30</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PBT glass-filled</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>1.53</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -3961,10 +4043,20 @@
           <t>POM (acetal)</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Acetal (POM)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>1.41</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -3981,10 +4073,20 @@
           <t>Aluminium ADC12 / A383</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Aluminium die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>2.74</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4001,10 +4103,16 @@
           <t>Aluminium A380</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aluminium die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
         <v>2.71</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4021,10 +4129,20 @@
           <t>Zinc Zamak 3</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Zinc die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>6.6</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4041,10 +4159,20 @@
           <t>Magnesium AZ91D</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Magnesium die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>1.81</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4061,10 +4189,20 @@
           <t>Grey cast iron FG260</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Grey cast iron</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>7.2</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4081,10 +4219,20 @@
           <t>SG / ductile iron</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ductile (SG) iron</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>7.1</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4101,10 +4249,20 @@
           <t>Cast steel</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cast steel</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>7.85</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4121,10 +4279,20 @@
           <t>Aluminium LM6 / A356</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Aluminium casting alloy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>2.68</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4141,10 +4309,20 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Copper casting alloy</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4161,10 +4339,20 @@
           <t>Mild steel CRCA / HR</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Carbon steel sheet</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>7.85</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4181,10 +4369,20 @@
           <t>Galvanised steel GI</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Coated steel sheet</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>7.85</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4201,10 +4399,20 @@
           <t>Stainless steel 304</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Stainless steel sheet</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>7.93</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4221,10 +4429,20 @@
           <t>Aluminium 5052</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Aluminium sheet</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>2.68</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4241,10 +4459,20 @@
           <t>Copper</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Copper sheet</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4261,10 +4489,20 @@
           <t>EPS bead grade S (20 kg/m3)</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EPS beads</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
         <v>0.02</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>EXAMPLE density. Foamed part density. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4281,10 +4519,16 @@
           <t>EPS bead grade F, flame retardant (25 kg/m3)</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EPS beads</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
         <v>0.025</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>EXAMPLE density. Foamed part density. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4301,10 +4545,20 @@
           <t>PET bottle grade (IV 0.80)</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PET resin</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>1.38</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>EXAMPLE density. Resin density, used for the shell weight. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4321,10 +4575,16 @@
           <t>rPET food grade</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PET resin</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
         <v>1.38</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>EXAMPLE density. Resin density. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4341,17 +4601,209 @@
           <t>PET preform grade</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PET resin</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>1.38</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>EXAMPLE density. For preform injection moulding. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PP copolymer (impact)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Polypropylene (PP)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PP talc filled 20 %</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Polypropylene (PP)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ABS flame retardant V0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PA66 GF30 heat stabilised</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Polyamide glass-filled (PA GF)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CRCA D513 EDD (deep drawing)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Carbon steel sheet</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Stainless steel 430</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Stainless steel sheet</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Aluminium AlSi10Mg (EN AC-43400)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Aluminium die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D28"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3767,8 +3767,106 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>trial_machine_process</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Press</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stage 23 try-out of dies: process name of the presses (Machines)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stage 23 die try-outs</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>trial_hours_each</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stage 23 press hours per try-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>trial_shots_each</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>200</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>strokes</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>EXAMPLE: Stage 23 strokes per try-out (material)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E134"/>
+  <autoFilter ref="A1:E138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -480,7 +480,6 @@
           <t>INR</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Currency shown on cost results</t>
@@ -1832,7 +1831,6 @@
           <t>Injection moulding</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Stage 4 try-out: process name of the machines (Machines sheet) the try-out machine is chosen from</t>
@@ -1930,7 +1928,6 @@
           <t>Die casting</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Stage 4 try-out: process name of the machines (Machines sheet) the try-out machine is chosen from</t>
@@ -2028,7 +2025,6 @@
           <t>operator</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>EXAMPLE: Labour grade of the moulding / casting operator (Labour grades)</t>
@@ -2201,7 +2197,6 @@
           <t>Press</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>EXAMPLE: Machines process that takes sheet-metal press tonnage</t>
@@ -2949,7 +2944,6 @@
           <t>1, 2, 3, 4, 6, 8</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>EXAMPLE: Allowed cavity counts</t>
@@ -3072,7 +3066,6 @@
           <t>EPS moulding</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>EXAMPLE: Machine process used for try-out</t>
@@ -3093,7 +3086,6 @@
       <c r="C107" t="n">
         <v>2</v>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>EXAMPLE: Try-outs</t>
@@ -3441,7 +3433,6 @@
           <t>1, 2, 4, 6, 8, 10, 12, 16</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>EXAMPLE: Allowed cavity counts</t>
@@ -3564,7 +3555,6 @@
           <t>Stretch blow moulding</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>EXAMPLE: Machine process used for try-out</t>
@@ -3585,7 +3575,6 @@
       <c r="C127" t="n">
         <v>3</v>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>EXAMPLE: Try-outs</t>
@@ -3783,7 +3772,6 @@
           <t>Press</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>EXAMPLE: Stage 23 try-out of dies: process name of the presses (Machines)</t>
@@ -3862,6 +3850,193 @@
       <c r="E138" t="inlineStr">
         <is>
           <t>EXAMPLE: Stage 23 strokes per try-out (material)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>large_sheet_length_mm</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>EXAMPLE: sheet / cut-to-length coil used when the blank does not fit the standard sheet (large parts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>large_sheet_width_mm</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>EXAMPLE: widest sheet / coil for large blanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>cavity_pressure_bar</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>EXAMPLE: no clamp force for sand moulds (pattern equipment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>clamp_safety_factor</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>EXAMPLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>trial_machine_process</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Foundry moulding</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>EXAMPLE: machine used for the pattern trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>trials</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>EXAMPLE: pattern trials</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>trial_hours_each</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>4</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>EXAMPLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>trial_shots_each</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>10</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>moulds</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>EXAMPLE</t>
         </is>
       </c>
     </row>

--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$138</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,6 +480,7 @@
           <t>INR</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Currency shown on cost results</t>
@@ -1831,6 +1832,7 @@
           <t>Injection moulding</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Stage 4 try-out: process name of the machines (Machines sheet) the try-out machine is chosen from</t>
@@ -1928,6 +1930,7 @@
           <t>Die casting</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Stage 4 try-out: process name of the machines (Machines sheet) the try-out machine is chosen from</t>
@@ -2025,6 +2028,7 @@
           <t>operator</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>EXAMPLE: Labour grade of the moulding / casting operator (Labour grades)</t>
@@ -2197,6 +2201,7 @@
           <t>Press</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>EXAMPLE: Machines process that takes sheet-metal press tonnage</t>
@@ -2944,6 +2949,7 @@
           <t>1, 2, 3, 4, 6, 8</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>EXAMPLE: Allowed cavity counts</t>
@@ -3066,6 +3072,7 @@
           <t>EPS moulding</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>EXAMPLE: Machine process used for try-out</t>
@@ -3086,6 +3093,7 @@
       <c r="C107" t="n">
         <v>2</v>
       </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>EXAMPLE: Try-outs</t>
@@ -3433,6 +3441,7 @@
           <t>1, 2, 4, 6, 8, 10, 12, 16</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>EXAMPLE: Allowed cavity counts</t>
@@ -3555,6 +3564,7 @@
           <t>Stretch blow moulding</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>EXAMPLE: Machine process used for try-out</t>
@@ -3575,6 +3585,7 @@
       <c r="C127" t="n">
         <v>3</v>
       </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>EXAMPLE: Try-outs</t>
@@ -3772,6 +3783,7 @@
           <t>Press</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>EXAMPLE: Stage 23 try-out of dies: process name of the presses (Machines)</t>
@@ -3942,6 +3954,7 @@
       <c r="C142" t="n">
         <v>1</v>
       </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>EXAMPLE</t>
@@ -3964,6 +3977,7 @@
           <t>Foundry moulding</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>EXAMPLE: machine used for the pattern trial</t>
@@ -3984,6 +3998,7 @@
       <c r="C144" t="n">
         <v>1</v>
       </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>EXAMPLE: pattern trials</t>
@@ -4041,7 +4056,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E138"/>
+  <autoFilter ref="A1:E146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4052,13 +4067,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4074,10 +4091,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>material_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>density_g_cm3</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -4094,10 +4121,20 @@
           <t>PP (polypropylene)</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Polypropylene (PP)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0.905</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4114,10 +4151,20 @@
           <t>ABS</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1.04</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4134,10 +4181,20 @@
           <t>PC (polycarbonate)</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Polycarbonate (PC)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1.2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4154,10 +4211,20 @@
           <t>PC/ABS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PC/ABS blend</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>1.13</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4174,10 +4241,20 @@
           <t>PA6</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Polyamide (PA)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>1.13</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4194,10 +4271,20 @@
           <t>PA66 GF30</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Polyamide glass-filled (PA GF)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>1.36</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4214,10 +4301,20 @@
           <t>PBT GF30</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PBT glass-filled</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>1.53</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4234,10 +4331,20 @@
           <t>POM (acetal)</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Acetal (POM)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>1.41</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4254,10 +4361,20 @@
           <t>Aluminium ADC12 / A383</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Aluminium die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>2.74</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4274,10 +4391,16 @@
           <t>Aluminium A380</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aluminium die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
         <v>2.71</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4294,10 +4417,20 @@
           <t>Zinc Zamak 3</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Zinc die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>6.6</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4314,10 +4447,20 @@
           <t>Magnesium AZ91D</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Magnesium die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>1.81</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4334,10 +4477,20 @@
           <t>Grey cast iron FG260</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Grey cast iron</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>7.2</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4354,10 +4507,20 @@
           <t>SG / ductile iron</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ductile (SG) iron</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>7.1</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4374,10 +4537,20 @@
           <t>Cast steel</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cast steel</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>7.85</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4394,10 +4567,20 @@
           <t>Aluminium LM6 / A356</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Aluminium casting alloy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>2.68</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4414,10 +4597,20 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Copper casting alloy</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4434,10 +4627,20 @@
           <t>Mild steel CRCA / HR</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Carbon steel sheet</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>7.85</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4454,10 +4657,20 @@
           <t>Galvanised steel GI</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Coated steel sheet</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>7.85</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4474,10 +4687,20 @@
           <t>Stainless steel 304</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Stainless steel sheet</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>7.93</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4494,10 +4717,20 @@
           <t>Aluminium 5052</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Aluminium sheet</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>2.68</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4514,10 +4747,20 @@
           <t>Copper</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Copper sheet</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Density: typical value - check your datasheet. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4534,10 +4777,20 @@
           <t>EPS bead grade S (20 kg/m3)</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EPS beads</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
         <v>0.02</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>EXAMPLE density. Foamed part density. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4554,10 +4807,16 @@
           <t>EPS bead grade F, flame retardant (25 kg/m3)</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EPS beads</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
         <v>0.025</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>EXAMPLE density. Foamed part density. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4574,10 +4833,20 @@
           <t>PET bottle grade (IV 0.80)</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PET resin</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>1.38</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>EXAMPLE density. Resin density, used for the shell weight. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4594,10 +4863,16 @@
           <t>rPET food grade</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PET resin</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
         <v>1.38</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>EXAMPLE density. Resin density. Rates: Rates page (material / material_scrap)</t>
         </is>
@@ -4614,17 +4889,209 @@
           <t>PET preform grade</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PET resin</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>1.38</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>EXAMPLE density. For preform injection moulding. Rates: Rates page (material / material_scrap)</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PP copolymer (impact)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Polypropylene (PP)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PP talc filled 20 %</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Polypropylene (PP)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ABS flame retardant V0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>plastic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PA66 GF30 heat stabilised</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Polyamide glass-filled (PA GF)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CRCA D513 EDD (deep drawing)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Carbon steel sheet</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Stainless steel 430</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Stainless steel sheet</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>die_casting</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Aluminium AlSi10Mg (EN AC-43400)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Aluminium die-cast alloy</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D28"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4055,8 +4055,521 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>machine_turned</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CNC-LATHE</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>EXAMPLE: machine of turned parts (Master data → Machines)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>machine_milled</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>VMC-850</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>EXAMPLE: machine of milled parts (Master data → Machines)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>turned_min_round_share</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>EXAMPLE: a part is turned when at least this share of its surface turns about one axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>hole_max_dia_mm</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>20</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>EXAMPLE: holes up to this diameter are drilled; bigger bores are machined</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>dia_allowance_mm</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>EXAMPLE: bar diameter above the largest turned diameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>face_allowance_mm</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>EXAMPLE: facing allowance at each end of a turned part</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>mill_allowance_mm</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>mm/side</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>EXAMPLE: stock on every side of a milled part</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>cut_off_mm</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>EXAMPLE: parting-off tool or saw kerf per part</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>bar_end_loss_pct</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>3</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>EXAMPLE: bar remnant and chucking loss on the stock weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>chip_recovery_pct</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>90</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>EXAMPLE: share of chips and remnant sold as scrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>setups_turned</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>set-ups</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>EXAMPLE: clampings of a turned part (both ends)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>setups_milled</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>set-ups</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>EXAMPLE: clampings of a milled part</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>load_unload_s</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>30</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>EXAMPLE: load, clamp and unload per set-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>setup_h</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>EXAMPLE: machine set-up per set-up and batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>batch_size</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>500</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>EXAMPLE: parts per batch (set-up shared by the batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>tool_change_pct</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>15</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>% of cutting</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>EXAMPLE: tool changes, rapid moves and measuring on top of the cutting time</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>drill_retract_s</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>s/hole</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>EXAMPLE: approach, peck and retract per drilled hole</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>fixture_factor_turned</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>EXAMPLE: turned parts need soft jaws only: share of the fixture rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>fixture_factor_milled</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>EXAMPLE: share of the fixture rate for a milled part</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>fixture_kg_per_setup</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>10</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>EXAMPLE: fixture weight per set-up (freight and duty of the fixture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>oee_pct</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>75</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>EXAMPLE: OEE of the CNC machines</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E146"/>
+  <autoFilter ref="A1:E167"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4067,7 +4580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5090,8 +5603,188 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Free-cutting steel EN1A (11SMnPb30)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Free-cutting steel bar</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Carbon steel EN8 (C45) bar</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Carbon steel bar</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alloy steel EN19 (42CrMo4) bar</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Alloy steel bar</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Stainless steel 304 bar</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Stainless steel bar</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Aluminium 6061-T6 bar</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Aluminium bar</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Brass CW614N (free-cutting) bar</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brass bar</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>EXAMPLE density and rates. Rates: Rates page (material / material_scrap)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F35"/>
+  <autoFilter ref="A1:F41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/master_data/master_data.xlsx
+++ b/master_data/master_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameters'!$A$1:$E$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Materials'!$A$1:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,11 +427,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
@@ -4568,8 +4568,258 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>stage_hit_time_s</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>6</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>EXAMPLE: one press hit with manual loading per stage die (stage 41 comparison)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>stage_operators_per_press</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>operators</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>EXAMPLE: operators per press for stage dies (manual load / unload)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>progressive_spm</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>30</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>strokes/min</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>EXAMPLE: strokes per minute of a coil-fed progressive die</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>progressive_operators</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>operators</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>EXAMPLE: operators per progressive press (coil fed, one operator for two presses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>stage_die_life_strokes</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>strokes</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>EXAMPLE: life of a stage die before replacement (one stroke per part)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>progressive_die_life_strokes</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>strokes</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>EXAMPLE: life of a progressive die before replacement (one stroke per part)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>compare_volume_min_factor</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>× volume</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>EXAMPLE: break-even chart from this share of the part's annual volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>compare_volume_max_factor</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>10</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>× volume</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>EXAMPLE: break-even chart up to this multiple of the part's annual volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>sheet_metal</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>compare_volume_points</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>9</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>EXAMPLE: volumes in the break-even table (spread evenly on a log scale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>machined</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>tool_life_shots</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>EXAMPLE: fixture life in parts before it is replaced (tool amortisation, stage 41)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E167"/>
+  <autoFilter ref="A1:E177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
